--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,276 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1096400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1337400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1494000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>957200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1107200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1493700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2020100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1397000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1612100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1743600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1951400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1113900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1230300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1188500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>682100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>619900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>665800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>662100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>895900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1096200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1224000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>790900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>918800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1218000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1652900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1146400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1347300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1430600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1590400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>942200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1009700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>979400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>559000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>508800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>550800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>539400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E10" s="3">
         <v>241200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>270000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>166300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>188400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>275700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>367200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>250600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>264800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>313000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>361000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>171700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>220600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>209100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>123100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>111100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>115000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>122700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E12" s="3">
         <v>45800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>45400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>48900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>63400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>81500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>107200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>108200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>105500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>89700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>73500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>96600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>39600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>33700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>34200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>38800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>38900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,55 +1081,58 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>30600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>21900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1124,67 +1143,73 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E15" s="3">
         <v>21300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>21200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>18700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1179400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1376300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1538600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1105600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1260000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1645500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2119400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1582500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1784200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1844100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1959200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1326500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1270500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1201800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>767700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>754100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>799100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>758300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-38900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-44600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-148400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-152800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-151800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-99300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-185500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-172100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-100500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-212600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-40200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-85600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-134200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-133300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-96200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1344,41 +1376,42 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1389,61 +1422,64 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-59900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-19800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-120600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-130300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-129700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-73600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-166700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-152800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-83700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-199100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1462,53 +1498,56 @@
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>700</v>
       </c>
       <c r="J22" s="3">
         <v>700</v>
       </c>
       <c r="K22" s="3">
+        <v>700</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1521,115 +1560,121 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-39300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-46200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-148700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-152800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-151600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-99700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-186100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-172700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-101100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-213100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-40600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-85100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-132700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-130600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-92600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-1300</v>
       </c>
       <c r="M24" s="3">
         <v>-1300</v>
       </c>
       <c r="N24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-900</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1639,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-83100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-46200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-148700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-153300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-151600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-98200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-186200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-173500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-99800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-212400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-39800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-84200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-132700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-130600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-92600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-83700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-150400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-158100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-154200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-101200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-188000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-174800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-99800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-212400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-39800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-84200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-132700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-130600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-92600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,41 +2118,44 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2097,81 +2166,87 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-83700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-150400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-158100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-154200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-101200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-188000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-174800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-99800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-212400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-39800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-84200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-132700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-130600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-92600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-83700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-150400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-158100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-154200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-101200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-188000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-174800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-99800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-212400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-39800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-84200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-132700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-130600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-92600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,47 +2483,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>166900</v>
+      </c>
+      <c r="E41" s="3">
         <v>220000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>335400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>363600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>361900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>354900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>430500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>475900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>618300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>791400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>810700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>329600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2457,8 +2543,11 @@
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,47 +2605,50 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E43" s="3">
         <v>75300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>94800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>97600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>94400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>119600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>81400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>104900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>114700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>106600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2575,8 +2667,11 @@
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,47 +2729,50 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54500</v>
+      </c>
+      <c r="E45" s="3">
         <v>62500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>63700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>72600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>76500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>92500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>109700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>104600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>94900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>84400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>73200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>66000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2693,47 +2791,50 @@
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E46" s="3">
         <v>357800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>493900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>533800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>517900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>541800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>659800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>693900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>794600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>980700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>998600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>502200</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2752,8 +2853,11 @@
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,47 +2915,50 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>560200</v>
+      </c>
+      <c r="E48" s="3">
         <v>583100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>610200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>647000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>675700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>686800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>682200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>671000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>642100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>610200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>584700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>580800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2870,47 +2977,50 @@
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>287400</v>
+      </c>
+      <c r="E49" s="3">
         <v>294900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>290200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>298400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>297700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>306200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>314200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>308900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>315500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>310100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>284800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>233700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
@@ -2929,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,47 +3163,50 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E52" s="3">
         <v>27800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>52700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>48400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>46200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3106,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,47 +3287,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1160300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1263600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1424600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1513900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1533100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1589100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1715400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1726500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1800600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1947200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1911600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1367200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3224,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,47 +3399,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E57" s="3">
         <v>22600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>36700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>34600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3329,47 +3459,50 @@
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E58" s="3">
         <v>27900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>180400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>254300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>181900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>36500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>16</v>
       </c>
@@ -3388,47 +3521,50 @@
       <c r="U58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E59" s="3">
         <v>287100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>307000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>293800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>307500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>362700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>374900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>348200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>386300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>368900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>308500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>256800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3447,47 +3583,50 @@
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>292500</v>
+      </c>
+      <c r="E60" s="3">
         <v>337600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>510700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>569900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>517500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>443900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>448800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>403200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>437100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>422900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>351400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>306900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3506,8 +3645,11 @@
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3565,47 +3707,50 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>435800</v>
+      </c>
+      <c r="E62" s="3">
         <v>448600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>462200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>482300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>494900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>503600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>510800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>517800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>515900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>494400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>484700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>468500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3624,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,47 +3955,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>731600</v>
+      </c>
+      <c r="E66" s="3">
         <v>789600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>977000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1055800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1016000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>951200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>963200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>924500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>956800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>922000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>836100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>775400</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>16</v>
       </c>
@@ -3860,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,11 +4204,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>1419100</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,47 +4289,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2517800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4178,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,47 +4537,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>428700</v>
+      </c>
+      <c r="E76" s="3">
         <v>474000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>447600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>458100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>517100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>637900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>752200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>802000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>843800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1025200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1075500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-827300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4414,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-83700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-150400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-158100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-154200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-101200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-188000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-174800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-99800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-212400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-39800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-84200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-132700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-130600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-92600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,47 +4816,48 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E83" s="3">
         <v>21300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4678,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,47 +5186,50 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="E89" s="3">
         <v>15000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>53300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-55500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-117800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-53600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-111000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-76900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>91400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-47300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5032,8 +5248,11 @@
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,47 +5274,48 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5114,8 +5334,11 @@
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,47 +5458,50 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-39300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-69200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5291,8 +5520,11 @@
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,47 +5792,50 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-128300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-78900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>60700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>138000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-64600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>444400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5609,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,47 +5916,50 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-115400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-75600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-142400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-173100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>481100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-110500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5725,6 +5976,9 @@
         <v>16</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1054100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1096400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1337400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1494000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>957200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1107200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1493700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2020100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1397000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1612100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1743600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1951400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1113900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1230300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1188500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>682100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>619900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>665800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>662100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>862300</v>
+      </c>
+      <c r="E9" s="3">
         <v>895900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1096200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1224000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>790900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>918800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1218000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1652900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1146400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1347300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1430600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1590400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>942200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1009700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>979400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>559000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>508800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>550800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>539400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>191800</v>
+      </c>
+      <c r="E10" s="3">
         <v>200500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>241200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>270000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>166300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>188400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>275700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>367200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>250600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>264800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>313000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>361000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>171700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>220600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>209100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>123100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>111100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>115000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>122700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E12" s="3">
         <v>44400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>45800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>45400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>48900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>63400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>81500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>107200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>108200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>105500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>89700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>73500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>96600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>39600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>33700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>34200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>38800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>38900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>34800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1084,58 +1101,61 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>13200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>30600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>21900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>24900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1146,70 +1166,76 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E15" s="3">
         <v>21500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>11100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1186200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1179400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1376300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1538600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1105600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1260000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1645500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2119400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1582500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1784200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1844100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1959200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1326500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1270500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1201800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>767700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>754100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>799100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>758300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-132100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-83000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-38900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-44600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-148400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-152800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-151800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-99300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-185500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-172100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-212600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-85600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-134200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-133300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-96200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1377,44 +1410,45 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1425,64 +1459,67 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-110200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-59900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-120600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-130300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-129700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-73600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-166700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-152800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-83700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-199100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1501,56 +1538,59 @@
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>700</v>
       </c>
       <c r="K22" s="3">
         <v>700</v>
       </c>
       <c r="L22" s="3">
+        <v>700</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1563,121 +1603,127 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-132500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-83000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-39300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-46200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-148700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-152800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-151600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-99700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-186100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-172700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-101100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-213100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-40600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-85100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-132700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-130600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-92600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-1300</v>
       </c>
       <c r="N24" s="3">
         <v>-1300</v>
       </c>
       <c r="O24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P24" s="3">
         <v>-700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-800</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-900</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-132200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-83100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-46200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-148700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-153300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-151600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-186200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-173500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-99800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-212400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-84200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-132700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-130600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-92600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-132900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-83700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-47800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-150400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-158100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-154200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-101200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-188000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-174800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-99800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-212400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-84200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-132700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-130600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-92600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,44 +2188,47 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2169,84 +2239,90 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-132900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-83700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-47800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-150400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-158100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-154200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-101200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-188000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-174800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-99800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-212400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-84200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-132700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-130600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-92600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-132900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-83700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-47800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-150400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-158100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-154200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-101200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-188000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-174800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-99800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-212400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-84200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-132700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-130600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-92600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,50 +2570,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E41" s="3">
         <v>166900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>220000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>335400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>363600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>361900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>354900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>430500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>475900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>618300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>791400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>810700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>329600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2546,8 +2633,11 @@
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,50 +2698,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E43" s="3">
         <v>60600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>75300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>94800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>97600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>79500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>94400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>119600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>81400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>104900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>114700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>106600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2670,8 +2763,11 @@
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2732,50 +2828,53 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E45" s="3">
         <v>54500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>62500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>63700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>72600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>76500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>92500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>109700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>94900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>84400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>73200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>66000</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2794,50 +2893,53 @@
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>292800</v>
+      </c>
+      <c r="E46" s="3">
         <v>282000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>357800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>493900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>533800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>517900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>541800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>659800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>693900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>794600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>980700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>998600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>502200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2856,8 +2958,11 @@
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2918,50 +3023,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E48" s="3">
         <v>560200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>583100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>610200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>647000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>675700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>686800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>682200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>671000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>642100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>610200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>584700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>580800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>16</v>
       </c>
@@ -2980,50 +3088,53 @@
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E49" s="3">
         <v>287400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>294900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>290200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>298400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>297700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>306200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>314200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>308900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>315500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>310100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>284800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>233700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,50 +3283,53 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E52" s="3">
         <v>30700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>54300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>52700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>46200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>50500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,50 +3413,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1144900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1160300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1263600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1424600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1513900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1533100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1589100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1715400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1726500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1800600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1947200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1911600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1367200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,50 +3530,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E57" s="3">
         <v>18400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>28100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3462,50 +3593,53 @@
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E58" s="3">
         <v>24800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>180400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>254300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>181900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>36500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>30400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>16</v>
       </c>
@@ -3524,50 +3658,53 @@
       <c r="V58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>321700</v>
+      </c>
+      <c r="E59" s="3">
         <v>249300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>287100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>307000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>293800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>307500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>362700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>374900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>348200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>386300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>368900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>308500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>256800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3586,50 +3723,53 @@
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>362200</v>
+      </c>
+      <c r="E60" s="3">
         <v>292500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>337600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>510700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>569900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>517500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>443900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>448800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>403200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>437100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>422900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>351400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>306900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3648,8 +3788,11 @@
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3710,50 +3853,53 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>449200</v>
+      </c>
+      <c r="E62" s="3">
         <v>435800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>448600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>462200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>482300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>494900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>503600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>510800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>517800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>515900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>494400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>484700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>468500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,50 +4113,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>814600</v>
+      </c>
+      <c r="E66" s="3">
         <v>731600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>789600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>977000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1055800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1016000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>951200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>963200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>924500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>956800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>922000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>836100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>775400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4207,11 +4375,11 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>1419100</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,50 +4463,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2650700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,50 +4723,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>330300</v>
+      </c>
+      <c r="E76" s="3">
         <v>428700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>474000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>447600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>458100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>517100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>637900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>752200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>802000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>843800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1025200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1075500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-827300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-132900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-83700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-47800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-150400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-158100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-154200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-101200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-188000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-174800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-99800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-212400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-84200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-132700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-130600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-92600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,50 +5015,51 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E83" s="3">
         <v>21500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>22300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>16</v>
       </c>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,50 +5403,53 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-38700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-55500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-117800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-53600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-111000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-76900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>91400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-47300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5251,8 +5468,11 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,50 +5495,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5470,41 +5700,41 @@
         <v>-3500</v>
       </c>
       <c r="E94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-69200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,50 +6038,53 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-128300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-78900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>60700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>138000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-64600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>444400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>6000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
@@ -5857,8 +6103,11 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5919,50 +6168,53 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-53100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-115400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-45400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-142400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-173100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>481100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-110500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
@@ -5979,6 +6231,9 @@
         <v>16</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1700600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1054100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1096400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1337400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1494000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>957200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1107200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1493700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2020100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1397000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1612100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1743600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1951400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1113900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1230300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1188500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>682100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>619900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>665800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>662100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1405300</v>
+      </c>
+      <c r="E9" s="3">
         <v>862300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>895900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1096200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1224000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>790900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>918800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1218000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1652900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1146400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1347300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1430600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1590400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>942200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1009700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>979400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>559000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>508800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>550800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>539400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>295300</v>
+      </c>
+      <c r="E10" s="3">
         <v>191800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>241200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>270000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>166300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>188400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>275700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>367200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>250600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>264800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>313000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>361000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>171700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>220600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>209100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>123100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>111100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>115000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>122700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E12" s="3">
         <v>47000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>44400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>45800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>45400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>48900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>63400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>81500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>107200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>108200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>105500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>89700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>73500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>96600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>33700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>34200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>38800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>38900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,61 +1121,64 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>13200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1169,73 +1189,79 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E15" s="3">
         <v>20800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>19300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>13500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>11800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>11100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1679300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1186200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1179400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1376300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1538600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1105600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1260000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1645500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2119400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1582500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1784200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1844100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1959200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1326500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1270500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1201800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>767700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>754100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>799100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>758300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-132100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-83000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-38900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-44600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-148400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-152800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-151800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-99300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-185500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-172100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-212600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-40200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-85600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-134200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-133300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-96200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,47 +1444,48 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1462,67 +1496,70 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-110200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-59900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-19800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-120600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-130300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-129700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-73600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-166700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-152800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-83700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-199100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1541,59 +1578,62 @@
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>700</v>
       </c>
       <c r="L22" s="3">
         <v>700</v>
       </c>
       <c r="M22" s="3">
+        <v>700</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
@@ -1606,127 +1646,133 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-132500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-83000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-46200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-148700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-152800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-151600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-99700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-186100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-172700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-101100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-213100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-40600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-85100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-132700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-130600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-92600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-1300</v>
       </c>
       <c r="O24" s="3">
         <v>-1300</v>
       </c>
       <c r="P24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-800</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-900</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-132200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-83100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-46200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-148700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-153300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-151600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-186200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-173500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-99800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-212400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-39800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-84200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-132700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-130600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-92600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-132900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-83700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-47800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-150400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-158100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-154200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-101200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-188000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-174800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-99800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-212400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-39800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-84200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-132700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-130600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-92600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,47 +2258,50 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2242,87 +2312,93 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-132900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-83700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-47800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-150400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-158100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-154200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-101200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-188000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-174800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-99800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-212400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-39800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-84200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-132700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-130600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-92600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-132900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-83700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-47800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-150400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-158100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-154200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-101200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-188000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-174800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-99800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-212400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-39800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-84200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-132700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-130600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-92600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,53 +2657,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>185800</v>
+      </c>
+      <c r="E41" s="3">
         <v>165900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>166900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>220000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>335400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>363600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>361900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>354900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>430500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>475900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>618300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>791400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>810700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>329600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2636,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,53 +2791,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E43" s="3">
         <v>78600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>60600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>75300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>94800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>97600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>94400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>119600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>81400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>104900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>114700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>106600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2831,53 +2927,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E45" s="3">
         <v>48300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>54500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>62500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>63700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>72600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>76500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>92500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>109700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>104600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>94900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>84400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>73200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>66000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2896,53 +2995,56 @@
       <c r="W45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>320500</v>
+      </c>
+      <c r="E46" s="3">
         <v>292800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>282000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>357800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>493900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>533800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>517900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>541800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>659800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>693900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>794600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>980700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>998600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>502200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>16</v>
       </c>
@@ -2961,8 +3063,11 @@
       <c r="W46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3026,53 +3131,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>541800</v>
+      </c>
+      <c r="E48" s="3">
         <v>540000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>560200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>583100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>610200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>647000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>675700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>686800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>682200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>671000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>642100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>610200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>584700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>580800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3091,53 +3199,56 @@
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>326300</v>
+      </c>
+      <c r="E49" s="3">
         <v>283900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>287400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>294900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>290200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>298400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>297700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>306200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>314200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>308900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>315500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>310100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>284800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>233700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,53 +3403,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E52" s="3">
         <v>28200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>34700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>54300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>59200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>52700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>48400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,53 +3539,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1215200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1144900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1160300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1263600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1424600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1513900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1533100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1589100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1715400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1726500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1800600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1947200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1911600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1367200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,53 +3661,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E57" s="3">
         <v>17000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>31800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>39900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3596,53 +3727,56 @@
       <c r="W57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E58" s="3">
         <v>23500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>24800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>27900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>180400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>254300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>181900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>36500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>30400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10200</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>16</v>
       </c>
@@ -3661,53 +3795,56 @@
       <c r="W58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>340700</v>
+      </c>
+      <c r="E59" s="3">
         <v>321700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>249300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>287100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>307000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>293800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>307500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>362700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>374900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>348200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>386300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>368900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>308500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>256800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3726,53 +3863,56 @@
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>385800</v>
+      </c>
+      <c r="E60" s="3">
         <v>362200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>292500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>337600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>510700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>569900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>517500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>443900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>448800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>403200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>437100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>422900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>351400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>306900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3791,8 +3931,11 @@
       <c r="W60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3856,53 +3999,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>427700</v>
+      </c>
+      <c r="E62" s="3">
         <v>449200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>435800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>448600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>462200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>482300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>494900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>503600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>510800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>517800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>515900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>494400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>484700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>468500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>16</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,53 +4271,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>816800</v>
+      </c>
+      <c r="E66" s="3">
         <v>814600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>731600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>789600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>977000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1055800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1016000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>951200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>963200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>924500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>956800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>922000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>836100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>775400</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4378,11 +4546,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>1419100</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2630000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,53 +4909,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>398400</v>
+      </c>
+      <c r="E76" s="3">
         <v>330300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>428700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>474000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>447600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>458100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>517100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>637900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>752200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>802000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>843800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1025200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1075500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-827300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-132900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-83700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-47800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-150400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-158100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-154200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-101200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-188000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-174800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-99800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-212400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-39800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-84200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-132700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-130600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-92600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,53 +5214,54 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E83" s="3">
         <v>20800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>19300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,53 +5620,56 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-38700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>53300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-55500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-117800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-53600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-111000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-76900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>91400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-47300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5471,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,53 +5716,54 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,53 +5918,56 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3500</v>
+        <v>-23000</v>
       </c>
       <c r="E94" s="3">
         <v>-3500</v>
       </c>
       <c r="F94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="G94" s="3">
         <v>-2100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,53 +6284,56 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-128300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-78900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>60700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>138000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-64600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>444400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6106,8 +6352,11 @@
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,53 +6420,56 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-53100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-115400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-75600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-142400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-173100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>481100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-110500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6234,6 +6486,9 @@
         <v>16</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>COMP</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1494000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1700600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1054100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1096400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1337400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1494000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>957200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1107200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1493700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2020100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1397000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1612100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1743600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1951400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1113900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1230300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1188500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>682100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>619900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>665800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>662100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1405300</v>
+        <v>1311700</v>
       </c>
       <c r="E9" s="3">
-        <v>862300</v>
+        <v>1488000</v>
       </c>
       <c r="F9" s="3">
-        <v>895900</v>
+        <v>941300</v>
       </c>
       <c r="G9" s="3">
-        <v>1096200</v>
+        <v>976100</v>
       </c>
       <c r="H9" s="3">
-        <v>1224000</v>
+        <v>1178600</v>
       </c>
       <c r="I9" s="3">
-        <v>790900</v>
+        <v>1307900</v>
       </c>
       <c r="J9" s="3">
+        <v>868900</v>
+      </c>
+      <c r="K9" s="3">
         <v>918800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1218000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1652900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1146400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1347300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1430600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1590400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>942200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1009700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>979400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>559000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>508800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>550800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>539400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>295300</v>
+        <v>182300</v>
       </c>
       <c r="E10" s="3">
-        <v>191800</v>
+        <v>212600</v>
       </c>
       <c r="F10" s="3">
-        <v>200500</v>
+        <v>112800</v>
       </c>
       <c r="G10" s="3">
-        <v>241200</v>
+        <v>120300</v>
       </c>
       <c r="H10" s="3">
-        <v>270000</v>
+        <v>158800</v>
       </c>
       <c r="I10" s="3">
-        <v>166300</v>
+        <v>186100</v>
       </c>
       <c r="J10" s="3">
+        <v>88300</v>
+      </c>
+      <c r="K10" s="3">
         <v>188400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>275700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>367200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>250600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>264800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>313000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>361000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>171700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>220600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>209100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>123100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>111100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>115000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>122700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E12" s="3">
         <v>47400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>47000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>44400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>45800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>45400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>63400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>81500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>108200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>105500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>89700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>73500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>96600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>39600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>33700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>38800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>38900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>34800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,64 +1141,67 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>4300</v>
+        <v>2200</v>
       </c>
       <c r="E14" s="3">
-        <v>1500</v>
+        <v>5600</v>
       </c>
       <c r="F14" s="3">
-        <v>2100</v>
+        <v>59000</v>
       </c>
       <c r="G14" s="3">
-        <v>2000</v>
+        <v>-3200</v>
       </c>
       <c r="H14" s="3">
-        <v>15000</v>
+        <v>2500</v>
       </c>
       <c r="I14" s="3">
+        <v>16400</v>
+      </c>
+      <c r="J14" s="3">
         <v>13200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>21900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1192,76 +1212,82 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>21400</v>
+        <v>20400</v>
       </c>
       <c r="E15" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F15" s="3">
         <v>20800</v>
       </c>
-      <c r="F15" s="3">
-        <v>21500</v>
-      </c>
       <c r="G15" s="3">
+        <v>26800</v>
+      </c>
+      <c r="H15" s="3">
         <v>21300</v>
       </c>
-      <c r="H15" s="3">
-        <v>22300</v>
-      </c>
       <c r="I15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="J15" s="3">
         <v>24900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>18700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>13000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>11800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>11100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1679300</v>
+        <v>1495200</v>
       </c>
       <c r="E17" s="3">
-        <v>1186200</v>
+        <v>1673700</v>
       </c>
       <c r="F17" s="3">
-        <v>1179400</v>
+        <v>1127200</v>
       </c>
       <c r="G17" s="3">
-        <v>1376300</v>
+        <v>1182600</v>
       </c>
       <c r="H17" s="3">
-        <v>1538600</v>
+        <v>1373800</v>
       </c>
       <c r="I17" s="3">
-        <v>1105600</v>
+        <v>1522200</v>
       </c>
       <c r="J17" s="3">
+        <v>1092400</v>
+      </c>
+      <c r="K17" s="3">
         <v>1260000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1645500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2119400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1582500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1784200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1844100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1959200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1326500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1270500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1201800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>767700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>754100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>799100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>758300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>21300</v>
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
-        <v>-132100</v>
+        <v>26900</v>
       </c>
       <c r="F18" s="3">
-        <v>-83000</v>
+        <v>-73100</v>
       </c>
       <c r="G18" s="3">
-        <v>-38900</v>
+        <v>-86200</v>
       </c>
       <c r="H18" s="3">
-        <v>-44600</v>
+        <v>-36400</v>
       </c>
       <c r="I18" s="3">
-        <v>-148400</v>
+        <v>-28200</v>
       </c>
       <c r="J18" s="3">
+        <v>-135200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-152800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-151800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-99300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-185500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-172100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-100500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-212600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-40200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-85600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-134200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-133300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-96200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1445,124 +1478,128 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>1400</v>
+        <v>-500</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>800</v>
+      </c>
+      <c r="G20" s="3">
+        <v>700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
+        <v>700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="M20" s="3">
+        <v>300</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>500</v>
+      </c>
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="W20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="W20" s="3">
-        <v>3600</v>
-      </c>
-      <c r="X20" s="3">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>44100</v>
+        <v>19700</v>
       </c>
       <c r="E21" s="3">
-        <v>-110200</v>
+        <v>47000</v>
       </c>
       <c r="F21" s="3">
-        <v>-59900</v>
+        <v>-53100</v>
       </c>
       <c r="G21" s="3">
-        <v>-16100</v>
+        <v>-60100</v>
       </c>
       <c r="H21" s="3">
-        <v>-19800</v>
+        <v>-15500</v>
       </c>
       <c r="I21" s="3">
-        <v>-120600</v>
+        <v>-8000</v>
       </c>
       <c r="J21" s="3">
+        <v>-111800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-130300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-129700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-73600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-166700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-152800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-83700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-199100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1581,62 +1618,65 @@
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
       </c>
       <c r="N22" s="3">
+        <v>700</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
@@ -1649,133 +1689,139 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>21100</v>
+        <v>-2200</v>
       </c>
       <c r="E23" s="3">
-        <v>-132500</v>
+        <v>20700</v>
       </c>
       <c r="F23" s="3">
-        <v>-83000</v>
+        <v>-133300</v>
       </c>
       <c r="G23" s="3">
-        <v>-39300</v>
+        <v>-83700</v>
       </c>
       <c r="H23" s="3">
-        <v>-46200</v>
+        <v>-39700</v>
       </c>
       <c r="I23" s="3">
-        <v>-148700</v>
+        <v>-46900</v>
       </c>
       <c r="J23" s="3">
+        <v>-150200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-152800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-151600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-99700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-186100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-172700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-101100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-213100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-40600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-85100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-132700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-130600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-92600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-1300</v>
       </c>
       <c r="P24" s="3">
         <v>-1300</v>
       </c>
       <c r="Q24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-800</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>21200</v>
+        <v>-1900</v>
       </c>
       <c r="E26" s="3">
-        <v>-132200</v>
+        <v>20800</v>
       </c>
       <c r="F26" s="3">
-        <v>-83100</v>
+        <v>-133000</v>
       </c>
       <c r="G26" s="3">
-        <v>-38800</v>
+        <v>-83800</v>
       </c>
       <c r="H26" s="3">
-        <v>-46200</v>
+        <v>-39200</v>
       </c>
       <c r="I26" s="3">
-        <v>-148700</v>
+        <v>-46900</v>
       </c>
       <c r="J26" s="3">
+        <v>-150200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-153300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-151600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-98200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-186200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-173500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-99800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-212400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-39800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-13500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-84200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-132700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-130600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-92600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>20700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-132900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-83700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-39400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-47800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-150400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-158100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-154200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-101200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-188000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-174800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-99800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-212400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-39800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-13500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-84200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-132700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-130600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-92600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1400</v>
+        <v>500</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="M32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="W32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-2900</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>20700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-132900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-83700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-39400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-47800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-150400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-158100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-154200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-101200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-188000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-174800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-99800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-212400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-39800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-13500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-84200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-132700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-130600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-92600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>20700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-132900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-83700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-39400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-47800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-150400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-158100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-154200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-101200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-188000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-174800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-99800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-212400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-39800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-13500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-84200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-132700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-130600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-92600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,56 +2744,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>211200</v>
+      </c>
+      <c r="E41" s="3">
         <v>185800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>165900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>166900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>220000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>335400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>363600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>361900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>354900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>430500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>475900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>618300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>791400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>810700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>329600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,56 +2884,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E43" s="3">
         <v>90000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>78600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>60600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>75300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>94800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>97600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>79500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>119600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>113400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>81400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>104900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>114700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>106600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2862,31 +2955,34 @@
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2930,56 +3026,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E45" s="3">
         <v>44700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48300</v>
       </c>
-      <c r="F45" s="3">
-        <v>54500</v>
-      </c>
       <c r="G45" s="3">
+        <v>32300</v>
+      </c>
+      <c r="H45" s="3">
         <v>62500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>72600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>76500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>92500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>109700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>104600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>94900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>84400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>73200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>66000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>16</v>
       </c>
@@ -2998,56 +3097,59 @@
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>330500</v>
+      </c>
+      <c r="E46" s="3">
         <v>320500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>292800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>282000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>357800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>493900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>533800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>517900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>541800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>659800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>693900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>794600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>980700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>998600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>502200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3066,31 +3168,34 @@
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>4400</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3134,56 +3239,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>524800</v>
+      </c>
+      <c r="E48" s="3">
         <v>541800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>540000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>560200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>583100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>610200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>647000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>675700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>686800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>682200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>671000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>642100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>610200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>584700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>580800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3202,56 +3310,59 @@
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>316800</v>
+      </c>
+      <c r="E49" s="3">
         <v>326300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>283900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>287400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>294900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>290200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>298400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>297700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>306200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>314200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>308900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>315500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>310100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>284800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>233700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,56 +3523,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E52" s="3">
         <v>26600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>28200</v>
       </c>
-      <c r="F52" s="3">
-        <v>30700</v>
-      </c>
       <c r="G52" s="3">
+        <v>26300</v>
+      </c>
+      <c r="H52" s="3">
         <v>27800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>34700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>52700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>48400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>50500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,56 +3665,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1199800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1215200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1144900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1160300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1263600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1424600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1513900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1533100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1589100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1715400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1726500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1800600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1947200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1911600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1367200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,56 +3792,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E57" s="3">
         <v>17800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>34600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>31800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3730,56 +3861,59 @@
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>27300</v>
+        <v>126200</v>
       </c>
       <c r="E58" s="3">
-        <v>23500</v>
+        <v>127500</v>
       </c>
       <c r="F58" s="3">
-        <v>24800</v>
+        <v>123100</v>
       </c>
       <c r="G58" s="3">
-        <v>27900</v>
+        <v>123700</v>
       </c>
       <c r="H58" s="3">
-        <v>180400</v>
+        <v>132100</v>
       </c>
       <c r="I58" s="3">
-        <v>254300</v>
+        <v>281800</v>
       </c>
       <c r="J58" s="3">
+        <v>353200</v>
+      </c>
+      <c r="K58" s="3">
         <v>181900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>36500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>30400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>16200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10200</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>16</v>
       </c>
@@ -3798,56 +3932,59 @@
       <c r="X58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>340700</v>
+        <v>3100</v>
       </c>
       <c r="E59" s="3">
-        <v>321700</v>
+        <v>3400</v>
       </c>
       <c r="F59" s="3">
-        <v>249300</v>
+        <v>2300</v>
       </c>
       <c r="G59" s="3">
-        <v>287100</v>
+        <v>47500</v>
       </c>
       <c r="H59" s="3">
-        <v>307000</v>
+        <v>5100</v>
       </c>
       <c r="I59" s="3">
-        <v>293800</v>
+        <v>7300</v>
       </c>
       <c r="J59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="K59" s="3">
         <v>307500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>362700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>374900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>348200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>386300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>368900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>308500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>256800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>16</v>
       </c>
@@ -3866,56 +4003,59 @@
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>358300</v>
+      </c>
+      <c r="E60" s="3">
         <v>385800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>362200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>292500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>337600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>510700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>569900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>517500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>443900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>448800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>403200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>437100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>422900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>351400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>306900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>16</v>
       </c>
@@ -3934,31 +4074,34 @@
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>382300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>397400</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>394200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>410200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>426100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>448100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>467100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4002,56 +4145,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>427700</v>
+        <v>28100</v>
       </c>
       <c r="E62" s="3">
-        <v>449200</v>
+        <v>30300</v>
       </c>
       <c r="F62" s="3">
-        <v>435800</v>
+        <v>55000</v>
       </c>
       <c r="G62" s="3">
-        <v>448600</v>
+        <v>25600</v>
       </c>
       <c r="H62" s="3">
-        <v>462200</v>
+        <v>22500</v>
       </c>
       <c r="I62" s="3">
-        <v>482300</v>
+        <v>14100</v>
       </c>
       <c r="J62" s="3">
+        <v>15200</v>
+      </c>
+      <c r="K62" s="3">
         <v>494900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>503600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>510800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>517800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>515900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>494400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>484700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>468500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,56 +4429,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>816800</v>
+        <v>768700</v>
       </c>
       <c r="E66" s="3">
-        <v>814600</v>
+        <v>813500</v>
       </c>
       <c r="F66" s="3">
-        <v>731600</v>
+        <v>811400</v>
       </c>
       <c r="G66" s="3">
-        <v>789600</v>
+        <v>728300</v>
       </c>
       <c r="H66" s="3">
-        <v>977000</v>
+        <v>786200</v>
       </c>
       <c r="I66" s="3">
-        <v>1055800</v>
+        <v>972900</v>
       </c>
       <c r="J66" s="3">
+        <v>1052200</v>
+      </c>
+      <c r="K66" s="3">
         <v>1016000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>951200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>963200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>924500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>956800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>922000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>836100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>775400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4549,11 +4717,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>1419100</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2631700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2630000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,56 +5095,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E76" s="3">
         <v>398400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>330300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>428700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>474000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>447600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>458100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>517100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>637900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>752200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>802000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>843800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1025200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1075500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-827300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>16</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>20700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-132900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-83700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-39400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-47800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-150400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-158100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-154200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-101200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-188000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-174800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-99800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-212400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-39800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-13500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-84200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-132700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-130600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-92600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,56 +5413,57 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>21400</v>
+        <v>21300</v>
       </c>
       <c r="E83" s="3">
-        <v>20800</v>
+        <v>17000</v>
       </c>
       <c r="F83" s="3">
-        <v>21500</v>
+        <v>24900</v>
       </c>
       <c r="G83" s="3">
-        <v>21300</v>
+        <v>11800</v>
       </c>
       <c r="H83" s="3">
-        <v>22300</v>
+        <v>21000</v>
       </c>
       <c r="I83" s="3">
-        <v>24900</v>
+        <v>25400</v>
       </c>
       <c r="J83" s="3">
+        <v>18700</v>
+      </c>
+      <c r="K83" s="3">
         <v>21200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>18700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>19300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,56 +5837,59 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E89" s="3">
         <v>45000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-38700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-55500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-117800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-53600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-111000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-76900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>91400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-47300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5726,47 +5947,47 @@
         <v>-4600</v>
       </c>
       <c r="E91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>16</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,56 +6148,59 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23000</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-3500</v>
       </c>
       <c r="F94" s="3">
         <v>-3500</v>
       </c>
       <c r="G94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-29600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-31600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-69200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,31 +6248,32 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,56 +6530,59 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-128300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-78900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>60700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>138000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-64600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>444400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6355,31 +6601,34 @@
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6423,56 +6672,59 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E102" s="3">
         <v>19900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-53100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-115400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-28200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-75600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-142400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-173100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>481100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-110500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>16</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>COMP</t>
   </si>
@@ -656,327 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1380400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1494000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1700600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1054100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1096400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1337400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1494000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>957200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1107200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1493700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2020100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1397000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1612100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1743600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1951400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1113900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1230300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1188500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>682100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>619900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>665800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>662100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1222400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1311700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1488000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>941300</v>
       </c>
-      <c r="G9" s="3">
-        <v>976100</v>
-      </c>
       <c r="H9" s="3">
+        <v>975900</v>
+      </c>
+      <c r="I9" s="3">
         <v>1178600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1307900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>868900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>918800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1218000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1652900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1146400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1347300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1430600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1590400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>942200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1009700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>979400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>559000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>508800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>550800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>539400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E10" s="3">
         <v>182300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>212600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>112800</v>
       </c>
-      <c r="G10" s="3">
-        <v>120300</v>
-      </c>
       <c r="H10" s="3">
+        <v>120500</v>
+      </c>
+      <c r="I10" s="3">
         <v>158800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>186100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>88300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>188400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>275700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>367200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>250600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>264800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>313000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>361000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>171700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>220600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>209100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>123100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>111100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>115000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>122700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E12" s="3">
         <v>47500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>47400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>47000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>44400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>45800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>45400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>48900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>63400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>81500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>107200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>108200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>105500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>89700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>73500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>96600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>39600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>33700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>34200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>38800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>38900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>34800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,67 +1160,70 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-52300</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>59000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H14" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>30600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>21900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1215,79 +1234,85 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E15" s="3">
         <v>20400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>18700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>13100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>11800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>11100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1473300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1495200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1673700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1127200</v>
       </c>
-      <c r="G17" s="3">
-        <v>1182600</v>
-      </c>
       <c r="H17" s="3">
+        <v>1182400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1373800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1522200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1092400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1260000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1645500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2119400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1582500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1784200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1844100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1959200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1326500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1270500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1201800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>767700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>754100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>799100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>758300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-73100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-86200</v>
-      </c>
       <c r="H18" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-36400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-135200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-152800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-151800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-99300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-185500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-172100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-212600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-40200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-85600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-134200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-133300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-96200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,53 +1511,54 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1536,73 +1569,76 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-71200</v>
+      </c>
+      <c r="E21" s="3">
         <v>19700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-53100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-60100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-59900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-15500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-111800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-130300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-129700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-73600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-166700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-152800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-83700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-199100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1621,65 +1657,68 @@
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
       </c>
       <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
@@ -1692,139 +1731,145 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-133300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-83700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-39700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-46900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-150200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-152800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-151600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-99700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-186100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-172700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-101100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-213100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-40600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-85100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-132700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-130600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-92600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-1300</v>
       </c>
       <c r="Q24" s="3">
         <v>-1300</v>
       </c>
       <c r="R24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="S24" s="3">
         <v>-700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-800</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-900</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -1834,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-133000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-83800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-39200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-46900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-150200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-153300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-151600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-98200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-186200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-173500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-212400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-39800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-13500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-84200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-132700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-130600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-92600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-132900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-83700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-39400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-47800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-150400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-158100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-154200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-101200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-188000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-174800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-212400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-39800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-13500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-84200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-132700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-130600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-92600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,53 +2397,56 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2388,93 +2457,99 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-132900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-83700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-39400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-47800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-150400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-158100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-154200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-101200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-188000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-174800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-212400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-39800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-13500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-84200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-132700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-130600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-92600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-132900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-83700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-39400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-47800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-150400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-158100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-154200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-101200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-188000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-174800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-212400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-39800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-13500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-84200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-132700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-130600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-92600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,59 +2830,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>223800</v>
+      </c>
+      <c r="E41" s="3">
         <v>211200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>185800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>165900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>166900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>220000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>335400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>363600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>361900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>354900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>430500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>475900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>618300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>791400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>810700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>329600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2816,8 +2902,11 @@
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,59 +2976,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E43" s="3">
         <v>80600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>90000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>78600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>60600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>75300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>94800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>97600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>94400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>119600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>113400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>81400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>104900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>114700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>106600</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>16</v>
       </c>
@@ -2958,8 +3050,11 @@
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2984,8 +3079,8 @@
       <c r="J44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3029,59 +3124,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E45" s="3">
         <v>38700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>44700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>62500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>76500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>92500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>109700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>104600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>94900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>84400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>73200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>66000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3100,59 +3198,62 @@
       <c r="Y45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E46" s="3">
         <v>330500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>320500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>292800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>282000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>357800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>493900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>533800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>517900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>541800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>659800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>693900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>794600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>980700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>998600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>502200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3171,13 +3272,16 @@
       <c r="Y46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>16</v>
+      <c r="D47" s="3">
+        <v>5700</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>16</v>
@@ -3185,8 +3289,8 @@
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="3">
-        <v>4400</v>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>16</v>
@@ -3197,8 +3301,8 @@
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3242,59 +3346,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>515200</v>
+      </c>
+      <c r="E48" s="3">
         <v>524800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>541800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>540000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>560200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>583100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>610200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>647000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>675700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>686800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>682200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>671000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>642100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>610200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>584700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>580800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3313,59 +3420,62 @@
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>307400</v>
+      </c>
+      <c r="E49" s="3">
         <v>316800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>326300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>283900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>287400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>294900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>290200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>298400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>297700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>306200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>314200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>308900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>315500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>310100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>284800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>233700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,59 +3642,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E52" s="3">
         <v>27700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28200</v>
       </c>
-      <c r="G52" s="3">
-        <v>26300</v>
-      </c>
       <c r="H52" s="3">
+        <v>30700</v>
+      </c>
+      <c r="I52" s="3">
         <v>27800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>34700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>54300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>52700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>48400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>43500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>50500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,59 +3790,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1178000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1199800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1215200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1144900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1160300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1263600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1424600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1513900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1533100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1589100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1715400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1726500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1800600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1947200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1911600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1367200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3739,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,59 +3922,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>44700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>34600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>31800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3864,59 +3994,62 @@
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E58" s="3">
         <v>126200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>127500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>123100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>123700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>132100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>281800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>353200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>181900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>36500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>30400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>16</v>
       </c>
@@ -3935,59 +4068,62 @@
       <c r="Y58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>307500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>362700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>374900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>348200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>386300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>368900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>308500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>256800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4006,59 +4142,62 @@
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>353200</v>
+      </c>
+      <c r="E60" s="3">
         <v>358300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>385800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>362200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>292500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>337600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>510700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>569900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>517500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>443900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>448800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>403200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>437100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>422900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>351400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>306900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4077,35 +4216,38 @@
       <c r="Y60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>380500</v>
+      </c>
+      <c r="E61" s="3">
         <v>382300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>397400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>394200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>410200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>426100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>448100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>467100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4148,59 +4290,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E62" s="3">
         <v>28100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>30300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>55000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>494900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>503600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>510800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>517800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>515900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>494400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>484700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>468500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,59 +4586,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>765600</v>
+      </c>
+      <c r="E66" s="3">
         <v>768700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>813500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>811400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>728300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>786200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>972900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1052200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1016000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>951200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>963200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>924500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>956800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>922000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>836100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>775400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4503,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4720,11 +4887,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>1419100</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4984,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2672200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2631700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2630000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
@@ -4885,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,59 +5280,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>409400</v>
+      </c>
+      <c r="E76" s="3">
         <v>428000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>398400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>330300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>428700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>474000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>447600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>458100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>517100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>637900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>752200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>802000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>843800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1025200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1075500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-827300</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5169,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-132900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-83700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-39400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-47800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-150400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-158100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-154200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-101200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-188000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-174800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-212400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-39800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-13500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-84200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-132700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-130600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-92600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,59 +5611,60 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E83" s="3">
         <v>21300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>18700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>19300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,59 +6053,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E89" s="3">
         <v>37400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-38700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-55500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-117800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-53600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-111000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-76900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>91400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-47300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>16</v>
       </c>
@@ -5911,8 +6127,11 @@
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,59 +6157,60 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4600</v>
+        <v>-3800</v>
       </c>
       <c r="E91" s="3">
         <v>-4600</v>
       </c>
       <c r="F91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="G91" s="3">
         <v>-2700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6009,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,59 +6377,62 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23000</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-3500</v>
       </c>
       <c r="G94" s="3">
         <v>-3500</v>
       </c>
       <c r="H94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-54700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-69200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6222,8 +6451,11 @@
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6275,8 +6508,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,59 +6775,62 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-128300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-78900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>60700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>138000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-64600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>444400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6604,8 +6849,11 @@
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6630,8 +6878,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6675,59 +6923,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E102" s="3">
         <v>25400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-53100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-115400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-75600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-45400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-142400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-173100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>481100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-110500</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6744,6 +6995,9 @@
         <v>16</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>COMP</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1356200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1380400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1494000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1700600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1054100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1096400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1337400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1494000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>957200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1107200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1493700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2020100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1397000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1612100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1743600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1951400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1113900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1230300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1188500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>682100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>619900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>665800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>662100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1202800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1222400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1311700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1488000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>941300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>975900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1178600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1307900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>868900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>918800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1218000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1652900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1146400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1347300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1430600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1590400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>942200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1009700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>979400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>559000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>508800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>550800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>539400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>153400</v>
+      </c>
+      <c r="E10" s="3">
         <v>158000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>182300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>212600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>112800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>120500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>158800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>186100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>188400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>275700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>367200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>250600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>264800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>313000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>361000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>171700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>220600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>209100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>123100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>111100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>115000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>122700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E12" s="3">
         <v>46900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>47500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>47400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>44400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>45800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>45400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>48900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>63400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>81500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>107200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>108200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>105500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>89700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>73500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>96600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>39600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>33700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>34200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>38800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>38900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>34800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,70 +1180,73 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-52300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5600</v>
       </c>
-      <c r="G14" s="3">
-        <v>59000</v>
-      </c>
       <c r="H14" s="3">
+        <v>59900</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>16400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>30600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>21900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>24900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1237,82 +1257,88 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E15" s="3">
         <v>21600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>20400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20500</v>
       </c>
-      <c r="G15" s="3">
-        <v>20800</v>
-      </c>
       <c r="H15" s="3">
+        <v>19900</v>
+      </c>
+      <c r="I15" s="3">
         <v>26800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>25400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>18700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>13500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>13000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>12400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>11800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>11100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1400700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1473300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1495200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1673700</v>
       </c>
-      <c r="G17" s="3">
-        <v>1127200</v>
-      </c>
       <c r="H17" s="3">
+        <v>1126300</v>
+      </c>
+      <c r="I17" s="3">
         <v>1182400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1373800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1522200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1092400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1260000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1645500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2119400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1582500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1784200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1844100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1959200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1326500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1270500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1201800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>767700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>754100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>799100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>758300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-92900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-73100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-72200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-86000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-135200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-152800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-151800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-99300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-185500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-172100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-212600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-40200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-85600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-134200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-133300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-96200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1512,56 +1545,57 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1572,76 +1606,79 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-71200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>47000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-53100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-59900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-111800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-130300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-129700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-73600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-166700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-152800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-83700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-199100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1660,68 +1697,71 @@
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>700</v>
       </c>
       <c r="P22" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
@@ -1734,145 +1774,151 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-133300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-83700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-150200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-152800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-151600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-99700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-186100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-172700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-101100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-213100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-40600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-13500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-85100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-132700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-130600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-92600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-1300</v>
       </c>
       <c r="R24" s="3">
         <v>-1300</v>
       </c>
       <c r="S24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="T24" s="3">
         <v>-700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-800</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-900</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-133000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-83800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-39200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-46900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-150200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-153300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-151600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-98200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-186200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-173500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-99800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-212400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-39800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-13500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-84200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-132700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-130600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-92600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-40500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-132900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-83700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-47800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-150400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-158100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-154200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-101200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-188000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-174800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-99800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-212400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-39800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-13500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-84200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-132700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-130600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-92600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,56 +2467,59 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2460,96 +2530,102 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-40500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-132900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-83700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-39400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-47800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-150400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-158100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-154200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-101200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-188000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-174800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-99800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-212400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-39800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-13500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-84200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-132700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-130600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-92600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-40500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-132900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-83700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-39400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-47800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-150400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-158100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-154200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-101200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-188000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-174800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-99800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-212400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-39800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-13500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-84200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-132700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-130600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-92600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,62 +2917,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E41" s="3">
         <v>223800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>211200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>185800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>165900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>166900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>220000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>335400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>363600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>361900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>354900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>430500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>475900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>618300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>791400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>810700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>329600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2905,8 +2992,11 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,62 +3069,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>102200</v>
+      </c>
+      <c r="E43" s="3">
         <v>73000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>80600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>90000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>78600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>60600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>75300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>94800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>97600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>119600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>113400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>81400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>104900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>114700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>106600</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3082,8 +3178,8 @@
       <c r="K44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3127,62 +3223,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E45" s="3">
         <v>23800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>48300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>62500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>63700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>76500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>92500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>109700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>104600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>94900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>84400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>73200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>66000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3201,62 +3300,65 @@
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E46" s="3">
         <v>330000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>330500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>320500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>292800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>282000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>357800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>493900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>533800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>517900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>541800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>659800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>693900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>794600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>980700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>998600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>502200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3275,17 +3377,20 @@
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3">
         <v>5700</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3304,8 +3409,8 @@
       <c r="K47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3349,62 +3454,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>529300</v>
+      </c>
+      <c r="E48" s="3">
         <v>515200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>524800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>541800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>540000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>560200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>583100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>610200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>647000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>675700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>686800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>682200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>671000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>642100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>610200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>584700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>580800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3423,62 +3531,65 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>708800</v>
+      </c>
+      <c r="E49" s="3">
         <v>307400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>316800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>326300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>283900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>287400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>294900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>290200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>298400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>297700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>306200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>314200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>308900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>315500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>310100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>284800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>233700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,62 +3762,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E52" s="3">
         <v>19700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>28200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>34700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>59200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>52700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>48400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>46200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>50500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,62 +3916,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1542600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1178000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1199800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1215200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1144900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1160300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1263600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1424600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1513900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1533100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1589100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1715400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1726500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1800600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1947200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1911600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1367200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,62 +4053,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E57" s="3">
         <v>13000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>21800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>44700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>31800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>39900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3997,62 +4128,65 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>174200</v>
+      </c>
+      <c r="E58" s="3">
         <v>117100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>126200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>127500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>123100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>123700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>132100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>281800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>353200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>181900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>30400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>16200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4071,62 +4205,65 @@
       <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E59" s="3">
         <v>89200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>307500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>362700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>374900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>348200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>386300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>368900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>308500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>256800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4145,62 +4282,65 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>486600</v>
+      </c>
+      <c r="E60" s="3">
         <v>353200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>358300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>385800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>362200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>292500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>337600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>510700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>569900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>517500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>443900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>448800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>403200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>437100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>422900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>351400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>306900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4219,38 +4359,41 @@
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>381900</v>
+      </c>
+      <c r="E61" s="3">
         <v>380500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>382300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>397400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>394200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>410200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>426100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>448100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>467100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4293,62 +4436,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E62" s="3">
         <v>31900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>55000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>494900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>503600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>510800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>517800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>515900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>494400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>484700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>468500</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,62 +4744,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>904700</v>
+      </c>
+      <c r="E66" s="3">
         <v>765600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>768700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>813500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>811400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>728300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>786200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>972900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1052200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1016000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>951200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>963200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>924500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>956800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>922000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>836100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>775400</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4890,11 +5058,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>1419100</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,62 +5158,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2722900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2672200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2631700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2630000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,62 +5466,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>635000</v>
+      </c>
+      <c r="E76" s="3">
         <v>409400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>428000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>398400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>330300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>428700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>474000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>447600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>458100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>517100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>637900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>752200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>802000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>843800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1025200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1075500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-827300</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-40500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-132900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-83700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-39400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-47800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-150400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-158100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-154200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-101200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-188000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-174800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-99800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-212400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-39800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-13500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-84200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-132700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-130600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-92600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,62 +5810,63 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E83" s="3">
         <v>14500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>24900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,62 +6270,65 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E89" s="3">
         <v>30500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>37400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>45000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-38700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-55500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-117800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-53600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-111000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-76900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>91400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-47300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,62 +6378,63 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-4600</v>
       </c>
       <c r="F91" s="3">
         <v>-4600</v>
       </c>
       <c r="G91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,62 +6607,65 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-164500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23000</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-3500</v>
       </c>
       <c r="H94" s="3">
         <v>-3500</v>
       </c>
       <c r="I94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-54700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-69200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6511,8 +6745,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,62 +7021,65 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-128300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-78900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>60700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>138000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>444400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6852,8 +7098,11 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6881,8 +7130,8 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6926,62 +7175,65 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-96800</v>
+      </c>
+      <c r="E102" s="3">
         <v>12600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>25400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-53100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-115400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-75600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-45400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-142400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-173100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>481100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-110500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>16</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>COMP</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2059600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1356200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1380400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1494000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1700600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1054100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1096400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1337400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1494000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>957200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1107200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1493700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2020100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1397000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1612100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1743600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1951400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1113900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1230300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1188500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>682100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>619900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>665800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>662100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1797100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1202800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1222400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1311700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1488000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>941300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>975900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1178600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1307900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>868900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>918800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1218000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1652900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1146400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1347300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1430600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1590400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>942200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1009700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>979400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>559000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>508800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>550800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>539400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>262500</v>
+      </c>
+      <c r="E10" s="3">
         <v>153400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>158000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>182300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>212600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>112800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>120500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>158800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>186100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>188400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>275700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>367200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>250600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>264800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>313000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>361000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>171700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>220600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>209100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>123100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>111100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>115000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>122700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E12" s="3">
         <v>49900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>46900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>47500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>47000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>44400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>45800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>45400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>48900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>63400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>81500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>107200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>108200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>105500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>89700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>73500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>96600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>39600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>33700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>34200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>38800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>38900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>34800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,73 +1200,76 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>9200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-52300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>59900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>16400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>30600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>21900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>24900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1260,85 +1280,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E15" s="3">
         <v>28800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>25400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>18700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>19300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>14900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>13500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>13100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>13000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>12700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>12400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>11800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>11100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2019600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1400700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1473300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1495200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1673700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1126300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1182400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1373800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1522200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1092400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1260000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1645500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2119400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1582500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1784200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1844100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1959200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1326500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1270500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1201800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>767700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>754100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>799100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>758300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-44500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-92900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>26900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-72200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-86000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-135200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-152800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-151800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-99300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-185500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-172100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-212600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-40200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-85600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-134200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-96200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,59 +1579,60 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1609,79 +1643,82 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-14900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-71200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>47000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-53100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-59900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-111800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-130300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-129700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-73600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-166700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-152800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-83700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-199100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1700,71 +1737,74 @@
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
       </c>
       <c r="Q22" s="3">
+        <v>700</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -1777,151 +1817,157 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-133300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-83700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-150200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-152800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-151600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-99700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-186100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-172700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-101100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-213100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-40600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-13500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-85100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-132700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-130600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-1300</v>
       </c>
       <c r="S24" s="3">
         <v>-1300</v>
       </c>
       <c r="T24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="U24" s="3">
         <v>-700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-800</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-900</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
@@ -1931,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-50800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-40400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-133000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-83800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-39200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-150200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-153300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-151600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-98200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-186200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-173500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-99800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-212400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-39800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-13500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-84200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-132700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-130600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-50700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-40500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-132900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-83700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-39400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-47800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-150400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-158100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-154200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-101200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-174800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-99800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-212400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-39800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-13500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-84200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-132700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-130600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,59 +2537,62 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2533,99 +2603,105 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-50700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-40500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-132900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-83700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-39400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-47800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-150400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-158100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-154200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-101200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-174800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-99800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-212400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-39800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-13500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-84200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-132700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-130600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-50700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-40500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-132900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-83700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-39400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-47800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-150400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-158100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-154200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-101200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-174800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-99800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-212400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-39800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-13500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-84200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-132700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-130600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,65 +3004,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E41" s="3">
         <v>127000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>223800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>211200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>185800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>165900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>166900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>220000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>335400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>363600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>361900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>354900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>430500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>475900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>618300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>791400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>810700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>329600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2995,8 +3082,11 @@
       <c r="AA41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,65 +3162,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E43" s="3">
         <v>102200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>73000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>80600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>90000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>78600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>60600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>75300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>94400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>119600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>113400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>81400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>104900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>114700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>106600</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3181,8 +3277,8 @@
       <c r="L44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3226,65 +3322,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E45" s="3">
         <v>40500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>62500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>63700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>72600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>76500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>92500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>109700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>104600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>94900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>84400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>73200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>66000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3303,65 +3402,68 @@
       <c r="AA45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>348400</v>
+      </c>
+      <c r="E46" s="3">
         <v>269700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>330000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>330500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>320500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>292800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>282000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>357800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>493900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>533800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>517900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>541800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>659800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>693900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>794600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>980700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>998600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>502200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3380,20 +3482,23 @@
       <c r="AA46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3">
         <v>5700</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3412,8 +3517,8 @@
       <c r="L47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3457,65 +3562,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>512700</v>
+      </c>
+      <c r="E48" s="3">
         <v>529300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>515200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>524800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>541800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>540000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>560200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>583100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>610200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>647000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>675700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>686800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>682200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>671000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>642100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>610200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>584700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>580800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3534,65 +3642,68 @@
       <c r="AA48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>695300</v>
+      </c>
+      <c r="E49" s="3">
         <v>708800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>307400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>316800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>326300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>283900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>287400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>294900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>290200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>298400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>297700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>306200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>314200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>308900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>315500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>310100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>284800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>233700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,65 +3882,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E52" s="3">
         <v>34800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>34700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>54300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>59200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>52700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>48400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>46200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>50500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,65 +4042,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1596100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1542600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1178000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1199800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1215200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1144900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1160300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1263600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1424600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1513900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1533100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1589100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1715400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1726500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1800600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1947200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1911600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1367200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,65 +4184,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E57" s="3">
         <v>15900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>21800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>28100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>44700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>35300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>31800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>39900</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4131,65 +4262,68 @@
       <c r="AA57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>181200</v>
+      </c>
+      <c r="E58" s="3">
         <v>174200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>117100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>126200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>127500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>123100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>123700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>132100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>281800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>353200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>181900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>30400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>16200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4208,8 +4342,11 @@
       <c r="AA58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4217,56 +4354,56 @@
         <v>5500</v>
       </c>
       <c r="E59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F59" s="3">
         <v>89200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>47500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>307500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>362700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>374900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>348200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>386300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>368900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>308500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>256800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4285,65 +4422,68 @@
       <c r="AA59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>473700</v>
+      </c>
+      <c r="E60" s="3">
         <v>486600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>353200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>358300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>385800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>362200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>292500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>337600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>510700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>569900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>517500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>443900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>448800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>403200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>437100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>422900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>351400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>306900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4362,41 +4502,44 @@
       <c r="AA60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>365500</v>
+      </c>
+      <c r="E61" s="3">
         <v>381900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>380500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>382300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>397400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>394200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>410200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>426100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>448100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>467100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4439,65 +4582,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E62" s="3">
         <v>36200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>55000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>494900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>503600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>510800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>517800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>515900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>494400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>484700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>468500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,65 +4902,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>870700</v>
+      </c>
+      <c r="E66" s="3">
         <v>904700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>765600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>768700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>813500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>811400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>728300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>786200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>972900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1052200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1016000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>951200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>963200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>924500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>956800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>922000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>836100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>775400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5061,11 +5229,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>1419100</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,65 +5332,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2683500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2722900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2672200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2631700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2630000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,65 +5652,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>719900</v>
+      </c>
+      <c r="E76" s="3">
         <v>635000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>409400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>428000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>398400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>330300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>428700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>474000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>447600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>458100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>517100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>637900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>752200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>802000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>843800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1025200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1075500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-827300</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-50700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-40500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-132900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-83700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-39400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-47800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-150400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-158100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-154200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-101200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-188000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-174800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-99800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-212400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-39800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-13500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-84200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-132700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-130600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-92600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,65 +6009,66 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E83" s="3">
         <v>19900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>24900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>19300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>16</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,65 +6487,68 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E89" s="3">
         <v>23100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>37400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>45000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-38700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>53300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-55500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-117800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-53600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-111000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-76900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>91400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-47300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,65 +6599,66 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-4600</v>
       </c>
       <c r="G91" s="3">
         <v>-4600</v>
       </c>
       <c r="H91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,65 +6837,68 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-164500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-3500</v>
       </c>
       <c r="I94" s="3">
         <v>-3500</v>
       </c>
       <c r="J94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-39300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-54700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-69200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6748,8 +6982,8 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,65 +7267,68 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E100" s="3">
         <v>44600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-128300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-78900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>60700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>138000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-64600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>444400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7101,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7133,8 +7382,8 @@
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7178,65 +7427,68 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-96800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-53100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-115400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-75600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-45400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-142400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-173100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>481100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-110500</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>16</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>COMP</t>
   </si>
@@ -656,378 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1699800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1846000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2059600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1356200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1380400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1494000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1700600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1054100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1096400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1337400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1494000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>957200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1107200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1493700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2020100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1397000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1612100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1743600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1951400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1113900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1230300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1188500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>682100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>619900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>665800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>662100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1613000</v>
+        <v>1498700</v>
       </c>
       <c r="E9" s="3">
+        <v>1613700</v>
+      </c>
+      <c r="F9" s="3">
         <v>1797100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1202800</v>
       </c>
-      <c r="G9" s="3">
-        <v>1222400</v>
-      </c>
       <c r="H9" s="3">
-        <v>1311700</v>
+        <v>1223100</v>
       </c>
       <c r="I9" s="3">
+        <v>1312100</v>
+      </c>
+      <c r="J9" s="3">
         <v>1488000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>941300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>975900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1178600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1307900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>868900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>918800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1218000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1652900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1146400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1347300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1430600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1590400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>942200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1009700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>979400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>559000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>508800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>550800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>539400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>233000</v>
+        <v>201100</v>
       </c>
       <c r="E10" s="3">
+        <v>232300</v>
+      </c>
+      <c r="F10" s="3">
         <v>262500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>153400</v>
       </c>
-      <c r="G10" s="3">
-        <v>158000</v>
-      </c>
       <c r="H10" s="3">
-        <v>182300</v>
+        <v>157300</v>
       </c>
       <c r="I10" s="3">
+        <v>181900</v>
+      </c>
+      <c r="J10" s="3">
         <v>212600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>120500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>158800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>186100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>88300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>188400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>275700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>367200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>250600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>264800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>313000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>361000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>171700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>220600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>209100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>123100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>111100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>115000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>122700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E12" s="3">
         <v>67400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>63400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>49900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>46900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>47500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>47400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>47000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>44400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>45800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>48900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>63400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>81500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>107200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>108200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>105500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>89700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>73500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>96600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>39600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>33700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>34200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>38800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>38900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>34800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,79 +1239,82 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>11300</v>
+        <v>12400</v>
       </c>
       <c r="E14" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9200</v>
       </c>
-      <c r="G14" s="3">
-        <v>-52300</v>
-      </c>
       <c r="H14" s="3">
-        <v>2200</v>
+        <v>10800</v>
       </c>
       <c r="I14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J14" s="3">
         <v>5600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>59900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>30600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>21900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>24900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1306,91 +1325,97 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E15" s="3">
         <v>27600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>28800</v>
       </c>
-      <c r="G15" s="3">
-        <v>21600</v>
-      </c>
       <c r="H15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="I15" s="3">
         <v>20400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>25400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>18700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>19300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>14900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>13500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>13100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>13000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>12700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>12400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>11100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1841900</v>
+        <v>1729300</v>
       </c>
       <c r="E17" s="3">
+        <v>1842600</v>
+      </c>
+      <c r="F17" s="3">
         <v>2019600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400700</v>
       </c>
-      <c r="G17" s="3">
-        <v>1473300</v>
-      </c>
       <c r="H17" s="3">
-        <v>1495200</v>
+        <v>1410200</v>
       </c>
       <c r="I17" s="3">
+        <v>1495600</v>
+      </c>
+      <c r="J17" s="3">
         <v>1673700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1126300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1182400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1373800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1522200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1092400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1260000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1645500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2119400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1582500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1784200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1844100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1959200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1326500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1270500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1201800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>767700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>754100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>799100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>758300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>4100</v>
+        <v>-29500</v>
       </c>
       <c r="E18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F18" s="3">
         <v>40000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-44500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-92900</v>
-      </c>
       <c r="H18" s="3">
-        <v>-1200</v>
+        <v>-29800</v>
       </c>
       <c r="I18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J18" s="3">
         <v>26900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-72200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-86000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-135200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-152800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-151800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-99300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-185500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-172100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-212600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-40200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-85600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-134200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-133300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-96200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1614,65 +1646,66 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1683,85 +1716,88 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>34700</v>
+        <v>-1800</v>
       </c>
       <c r="E21" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F21" s="3">
         <v>71100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-71200</v>
-      </c>
       <c r="H21" s="3">
-        <v>19700</v>
+        <v>-10100</v>
       </c>
       <c r="I21" s="3">
+        <v>19300</v>
+      </c>
+      <c r="J21" s="3">
         <v>47000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-53100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-59900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-111800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-130300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-129700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-73600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-166700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-152800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-83700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-199100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1780,77 +1816,80 @@
       <c r="AC21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>700</v>
       </c>
       <c r="S22" s="3">
+        <v>700</v>
+      </c>
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
@@ -1863,163 +1902,169 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-133300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-83700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-150200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-152800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-151600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-99700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-186100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-172700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-101100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-213100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-40600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-85100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-132700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-130600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-3400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-1300</v>
       </c>
       <c r="U24" s="3">
         <v>-1300</v>
       </c>
       <c r="V24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="W24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-800</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-900</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
@@ -2029,8 +2074,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-50800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-133000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-83800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-39200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-150200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-153300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-151600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-98200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-186200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-173500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-99800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-212400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-39800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-132700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-130600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-50700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-132900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-83700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-39400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-47800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-150400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-158100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-154200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-101200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-188000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-174800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-99800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-212400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-39800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-130600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,65 +2676,68 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2679,105 +2748,111 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-50700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-132900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-83700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-39400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-47800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-150400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-158100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-154200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-101200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-188000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-174800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-99800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-212400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-39800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-130600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-50700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-132900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-83700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-39400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-47800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-150400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-158100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-154200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-101200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-188000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-174800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-99800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-212400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-39800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-130600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,71 +3177,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>199000</v>
+      </c>
+      <c r="E41" s="3">
         <v>170300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>177300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>127000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>223800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>211200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>185800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>165900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>166900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>220000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>335400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>363600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>361900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>354900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>430500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>475900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>618300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>791400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>810700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>329600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3175,8 +3261,11 @@
       <c r="AC41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,71 +3347,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E43" s="3">
         <v>106000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>135200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>102200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>73000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>80600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>90000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>78600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>60600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>75300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>97600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>119600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>113400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>81400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>104900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>114700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>106600</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3341,8 +3433,11 @@
       <c r="AC43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3379,8 +3474,8 @@
       <c r="N44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3424,71 +3519,74 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E45" s="3">
         <v>37000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40500</v>
       </c>
-      <c r="G45" s="3">
-        <v>23800</v>
-      </c>
       <c r="H45" s="3">
+        <v>33200</v>
+      </c>
+      <c r="I45" s="3">
         <v>38700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>62500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>63700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>72600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>76500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>92500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>109700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>104600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>94900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>84400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>73200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>66000</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3507,71 +3605,74 @@
       <c r="AC45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>317200</v>
+      </c>
+      <c r="E46" s="3">
         <v>313300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>348400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>269700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>330000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>330500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>320500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>292800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>282000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>357800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>493900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>533800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>517900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>541800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>659800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>693900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>794600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>980700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>998600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>502200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3590,13 +3691,16 @@
       <c r="AC46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>16</v>
+      <c r="D47" s="3">
+        <v>14400</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>16</v>
@@ -3604,8 +3708,8 @@
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G47" s="3">
-        <v>5700</v>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>16</v>
@@ -3628,8 +3732,8 @@
       <c r="N47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3673,71 +3777,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>494900</v>
+      </c>
+      <c r="E48" s="3">
         <v>496800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>512700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>529300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>515200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>524800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>541800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>540000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>560200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>583100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>610200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>647000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>675700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>686800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>682200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>671000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>642100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>610200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>584700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>580800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3756,71 +3863,74 @@
       <c r="AC48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>672500</v>
+      </c>
+      <c r="E49" s="3">
         <v>691200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>695300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>708800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>307400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>316800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>326300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>283900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>287400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>294900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>290200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>298400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>297700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>306200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>314200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>308900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>315500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>310100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>284800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>233700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3839,8 +3949,11 @@
       <c r="AC49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,71 +4121,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E52" s="3">
         <v>52200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34800</v>
       </c>
-      <c r="G52" s="3">
-        <v>19700</v>
-      </c>
       <c r="H52" s="3">
+        <v>25400</v>
+      </c>
+      <c r="I52" s="3">
         <v>27700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>54300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>59200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>48400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>46200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>43500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>50500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4088,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,71 +4293,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1539500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1553500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1596100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1542600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1178000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1199800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1215200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1144900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1160300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1263600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1424600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1513900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1533100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1589100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1715400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1726500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1800600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1947200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1911600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1367200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4254,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,71 +4445,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E57" s="3">
         <v>15300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>21800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>44700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>43500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>34600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>35300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>31800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39900</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4399,71 +4529,74 @@
       <c r="AC57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E58" s="3">
         <v>128600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>181200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>174200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>117100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>126200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>127500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>123100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>123700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>132100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>281800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>353200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>181900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>36500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>30400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>16200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4482,71 +4615,74 @@
       <c r="AC58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>5500</v>
       </c>
       <c r="F59" s="3">
         <v>5500</v>
       </c>
       <c r="G59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H59" s="3">
         <v>89200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>307500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>362700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>374900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>348200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>386300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>368900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>308500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>256800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4565,71 +4701,74 @@
       <c r="AC59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>367300</v>
+      </c>
+      <c r="E60" s="3">
         <v>391000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>473700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>486600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>353200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>358300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>385800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>362200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>292500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>337600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>510700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>569900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>517500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>443900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>448800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>403200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>437100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>422900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>351400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>306900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4648,47 +4787,50 @@
       <c r="AC60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>354200</v>
+      </c>
+      <c r="E61" s="3">
         <v>352400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>365500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>381900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>380500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>382300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>397400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>394200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>410200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>426100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>448100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>467100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4731,71 +4873,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E62" s="3">
         <v>31700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>55000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>494900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>503600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>510800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>517800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>515900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>494400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>484700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>468500</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4814,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,71 +5217,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>752200</v>
+      </c>
+      <c r="E66" s="3">
         <v>775100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>870700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>904700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>765600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>768700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>813500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>811400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>728300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>786200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>972900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1052200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1016000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>951200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>963200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>924500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>956800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>922000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>836100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>775400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5146,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5403,11 +5570,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>1419100</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,71 +5679,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2730700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2688100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2683500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2722900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2672200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2631700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2630000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5592,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,71 +6023,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>782000</v>
+      </c>
+      <c r="E76" s="3">
         <v>773300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>719900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>635000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>409400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>428000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>398400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>330300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>428700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>474000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>447600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>458100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>517100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>637900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>752200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>802000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>843800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1025200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1075500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-827300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5924,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-50700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-132900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-83700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-39400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-47800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-150400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-158100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-154200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-101200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-188000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-174800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-99800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-212400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-39800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-84200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-130600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-92600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,71 +6406,72 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E83" s="3">
         <v>20400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19900</v>
       </c>
-      <c r="G83" s="3">
-        <v>14500</v>
-      </c>
       <c r="H83" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I83" s="3">
         <v>21300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>21000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>18700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>18700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>19300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6292,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,71 +6920,74 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E89" s="3">
         <v>75500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>72800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>37400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>45000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-38700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>53300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-55500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-117800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-111000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-76900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>91400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-47300</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6790,8 +7006,11 @@
       <c r="AC89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,71 +7040,72 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-4600</v>
       </c>
       <c r="I91" s="3">
         <v>-4600</v>
       </c>
       <c r="J91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-16500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>16</v>
       </c>
@@ -6904,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,71 +7296,74 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-164500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23000</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-3500</v>
       </c>
       <c r="K94" s="3">
         <v>-3500</v>
       </c>
       <c r="L94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="M94" s="3">
         <v>-2100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-29600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-54700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-69200</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7153,8 +7382,11 @@
       <c r="AC94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7222,8 +7455,8 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7267,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,71 +7758,74 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-75400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>44600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-128300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-78900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>60700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>138000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-64600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>444400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7599,8 +7844,11 @@
       <c r="AC100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7637,8 +7885,8 @@
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7682,71 +7930,74 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>50300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-96800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-53100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-115400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-28200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-75600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-45400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-142400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-173100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>481100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-110500</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7763,6 +8014,9 @@
         <v>16</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COMP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>COMP</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2704000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1699800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1846000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2059600</v>
       </c>
-      <c r="G8" s="3">
-        <v>1356200</v>
-      </c>
       <c r="H8" s="3">
+        <v>1356000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1380400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1494000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1700600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1054100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1096400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1337400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1494000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>957200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1107200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1493700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2020100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1397000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1612100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1743600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1951400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1113900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1230300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1188500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>682100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>619900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>665800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>662100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>716200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2334000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1498700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1613700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1797100</v>
       </c>
-      <c r="G9" s="3">
-        <v>1202800</v>
-      </c>
       <c r="H9" s="3">
+        <v>1203000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1223100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1312100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1488000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>941300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>975900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1178600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1307900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>868900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>918800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1218000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1652900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1146400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1347300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1430600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1590400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>942200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1009700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>979400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>559000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>508800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>550800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>539400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E10" s="3">
         <v>201100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>232300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>262500</v>
       </c>
-      <c r="G10" s="3">
-        <v>153400</v>
-      </c>
       <c r="H10" s="3">
+        <v>153000</v>
+      </c>
+      <c r="I10" s="3">
         <v>157300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>181900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>212600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>120500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>158800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>186100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>88300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>188400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>275700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>367200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>250600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>264800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>313000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>361000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>171700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>220600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>209100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>123100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>111100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>115000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>122700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E12" s="3">
         <v>65100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>67400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>63400</v>
       </c>
-      <c r="G12" s="3">
-        <v>49900</v>
-      </c>
       <c r="H12" s="3">
+        <v>50000</v>
+      </c>
+      <c r="I12" s="3">
         <v>46900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>47500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>47400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>47000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>44400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>45400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>48900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>63400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>81500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>107200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>108200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>105500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>89700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>73500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>96600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>39600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>33700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>34200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>38800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>38900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>34800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>32300</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,82 +1259,85 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E14" s="3">
         <v>12400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>9200</v>
-      </c>
       <c r="H14" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I14" s="3">
         <v>10800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>59900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>30600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>21900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>24900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1328,94 +1348,100 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E15" s="3">
         <v>26100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29400</v>
       </c>
-      <c r="G15" s="3">
-        <v>28800</v>
-      </c>
       <c r="H15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="I15" s="3">
         <v>19600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>24900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>21200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>25400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>18700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>19300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>14900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>13500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>13100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>13000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>12700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>12400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>11800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>11100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2858000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1729300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1842600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2019600</v>
       </c>
-      <c r="G17" s="3">
-        <v>1400700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1401000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1410200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1495600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1673700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1126300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1182400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1373800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1522200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1092400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1260000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1645500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2119400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1582500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1784200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1844100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1959200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1326500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1270500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1201800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>767700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>754100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>799100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>758300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>784400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>40000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-44500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-45000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-29800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-72200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-86000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-135200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-152800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-151800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-99300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-185500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-172100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-212600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-134200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-133300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-96200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-68200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1647,68 +1680,69 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-800</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1719,88 +1753,91 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>34000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>71100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-14900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-10100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-53100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-59900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-111800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-130300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-129700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-73600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-166700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-152800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-83700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-199100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1819,80 +1856,83 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2700</v>
       </c>
-      <c r="G22" s="3">
-        <v>2300</v>
-      </c>
       <c r="H22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>700</v>
       </c>
       <c r="S22" s="3">
         <v>700</v>
       </c>
       <c r="T22" s="3">
+        <v>700</v>
+      </c>
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
@@ -1905,169 +1945,175 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-379000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-54200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-40200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-133300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-83700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-39700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-150200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-152800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-151600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-99700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-186100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-172700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-101100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-213100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-40600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-85100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-132700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-130600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-401000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
-        <v>-3400</v>
-      </c>
       <c r="H24" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-1300</v>
       </c>
       <c r="V24" s="3">
         <v>-1300</v>
       </c>
       <c r="W24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-800</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-900</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
@@ -2077,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>39200</v>
       </c>
-      <c r="G26" s="3">
-        <v>-50800</v>
-      </c>
       <c r="H26" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-40400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-133000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-83800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-39200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-46900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-150200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-153300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-151600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-98200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-186200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-173500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-99800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-212400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-132700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-130600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>39400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-50700</v>
-      </c>
       <c r="H27" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-40500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-132900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-83700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-39400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-47800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-150400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-158100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-154200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-101200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-188000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-174800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-99800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-212400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-132700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-130600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,68 +2746,71 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1700</v>
       </c>
-      <c r="G32" s="3">
-        <v>800</v>
-      </c>
       <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2751,108 +2821,114 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>39400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-50700</v>
-      </c>
       <c r="H33" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-40500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-132900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-83700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-39400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-47800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-150400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-158100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-154200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-101200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-188000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-174800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-99800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-212400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-132700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-130600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>39400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-50700</v>
-      </c>
       <c r="H35" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-40500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-132900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-83700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-39400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-47800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-150400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-158100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-154200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-101200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-188000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-174800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-99800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-212400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-132700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-130600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,74 +3264,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>484000</v>
+      </c>
+      <c r="E41" s="3">
         <v>199000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>170300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>177300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>127000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>223800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>211200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>185800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>165900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>166900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>220000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>335400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>363600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>361900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>354900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>430500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>475900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>618300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>791400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>810700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>329600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3264,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,74 +3440,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E43" s="3">
         <v>82000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>106000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>102200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>73000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>80600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>90000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>78600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>60600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>75300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>94800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>79500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>119600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>113400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>81400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>104900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>114700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>106600</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3477,8 +3573,8 @@
       <c r="O44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3522,74 +3618,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>239000</v>
+      </c>
+      <c r="E45" s="3">
         <v>36200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>62500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>63700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>76500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>92500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>109700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>104600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>94900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>84400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>73200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>66000</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3608,74 +3707,77 @@
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1063000</v>
+      </c>
+      <c r="E46" s="3">
         <v>317200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>313300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>348400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>269700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>330000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>330500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>320500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>292800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>282000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>357800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>493900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>533800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>517900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>541800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>659800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>693900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>794600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>980700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>998600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>502200</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3694,17 +3796,20 @@
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E47" s="3">
         <v>14400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3735,8 +3840,8 @@
       <c r="O47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3780,74 +3885,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>926000</v>
+      </c>
+      <c r="E48" s="3">
         <v>494900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>496800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>512700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>529300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>515200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>524800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>541800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>540000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>560200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>583100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>610200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>647000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>675700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>686800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>682200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>671000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>642100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>610200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>584700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>580800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3866,74 +3974,77 @@
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5646000</v>
+      </c>
+      <c r="E49" s="3">
         <v>672500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>691200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>695300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>708800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>307400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>316800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>326300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>283900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>287400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>294900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>290200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>298400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>297700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>306200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>314200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>308900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>315500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>310100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>284800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>233700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>16</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,74 +4241,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>298000</v>
+      </c>
+      <c r="E52" s="3">
         <v>40500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>52200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>34800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>27800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>34700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>54300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>59200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>52700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>48400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>46200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>43500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>50500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,74 +4419,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8117000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1539500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1553500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1596100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1542600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1178000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1199800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1215200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1144900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1160300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1263600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1424600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1513900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1533100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1589100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1715400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1726500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1800600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1947200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1911600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1367200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,74 +4576,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>23300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>21800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>28100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>36700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>35300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>31800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>39900</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4532,74 +4663,77 @@
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E58" s="3">
         <v>122000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>128600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>181200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>174200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>117100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>126200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>127500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>123100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>123700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>132100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>281800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>353200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>181900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>36500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>30400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>18300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>16200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>18700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>10200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4618,74 +4752,77 @@
       <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E59" s="3">
         <v>77000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>5500</v>
       </c>
       <c r="G59" s="3">
         <v>5500</v>
       </c>
       <c r="H59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I59" s="3">
         <v>89200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>47500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>307500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>362700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>374900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>348200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>386300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>368900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>308500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>256800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4704,74 +4841,77 @@
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1262000</v>
+      </c>
+      <c r="E60" s="3">
         <v>367300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>391000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>473700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>486600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>353200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>358300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>385800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>362200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>292500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>337600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>510700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>569900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>517500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>443900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>448800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>403200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>437100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>422900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>351400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>306900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4790,50 +4930,53 @@
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3736000</v>
+      </c>
+      <c r="E61" s="3">
         <v>354200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>352400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>365500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>381900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>380500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>382300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>397400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>394200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>410200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>426100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>448100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>467100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4876,74 +5019,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E62" s="3">
         <v>30700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>494900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>503600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>510800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>517800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>515900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>494400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>484700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>468500</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,74 +5375,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5289000</v>
+      </c>
+      <c r="E66" s="3">
         <v>752200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>775100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>870700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>904700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>765600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>768700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>813500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>811400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>728300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>786200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>972900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1052200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1016000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>951200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>963200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>924500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>956800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>922000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>836100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>775400</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5573,11 +5741,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>1419100</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,74 +5853,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2709000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2730700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2688100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2683500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2722900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2672200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2631700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2630000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2650700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2517800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2434100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2346900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2196500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2038400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1884200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1783000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1595000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1420200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1320400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1313300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,74 +6209,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2820000</v>
+      </c>
+      <c r="E76" s="3">
         <v>782000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>773300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>719900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>635000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>409400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>428000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>398400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>330300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>428700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>474000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>447600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>458100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>517100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>637900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>752200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>802000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>843800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1025200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1075500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-827300</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>39400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-50700</v>
-      </c>
       <c r="H81" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-40500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-132900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-83700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-39400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-47800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-150400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-158100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-154200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-101200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-188000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-174800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-99800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-212400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-84200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-132700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-130600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-92600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-65300</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,74 +6605,75 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E83" s="3">
         <v>8000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>20500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>21000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>18700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>19300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>16700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13500</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,74 +7137,77 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-157000</v>
+      </c>
+      <c r="E89" s="3">
         <v>45300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>75500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>72800</v>
       </c>
-      <c r="G89" s="3">
-        <v>23100</v>
-      </c>
       <c r="H89" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I89" s="3">
         <v>30500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>37400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>45000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-38700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>53300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-55500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-117800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-53600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-111000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-76900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>91400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-47300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,74 +7261,75 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-3600</v>
-      </c>
       <c r="H91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-4600</v>
       </c>
       <c r="J91" s="3">
         <v>-4600</v>
       </c>
       <c r="K91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L91" s="3">
         <v>-2700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>16</v>
       </c>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,74 +7526,77 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-164500</v>
-      </c>
       <c r="H94" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-23000</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-3500</v>
       </c>
       <c r="L94" s="3">
         <v>-3500</v>
       </c>
       <c r="M94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-31600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-69200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7458,8 +7692,8 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,74 +8004,77 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>798000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-75400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5100</v>
       </c>
-      <c r="G100" s="3">
-        <v>44600</v>
-      </c>
       <c r="H100" s="3">
+        <v>45000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-14100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-128300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-78900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>60700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>138000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-64600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>13500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>444400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7847,8 +8093,11 @@
       <c r="AD100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7888,8 +8137,8 @@
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7933,74 +8182,77 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E102" s="3">
         <v>28700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>50300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-96800</v>
-      </c>
       <c r="H102" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="I102" s="3">
         <v>12600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-53100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-115400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-28200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-75600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-45400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-142400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-173100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-19300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>481100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-110500</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8017,6 +8269,9 @@
         <v>16</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
